--- a/artfynd/S 1231-2025 artfynd.xlsx
+++ b/artfynd/S 1231-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY168"/>
+  <dimension ref="A1:AZ168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629969</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637502</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637503</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638661</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638662</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639831</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639832</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639833</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639834</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639835</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118844223</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/299649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805608</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2410,6 +2495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637500</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637501</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2608,6 +2703,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639828</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,6 +2809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638658</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/485966</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/485967</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3013,6 +3128,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478771</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3119,6 +3239,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478772</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478775</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639808</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639809</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3516,6 +3656,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638620</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3613,6 +3758,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641111</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3719,6 +3869,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791827</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3829,6 +3984,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103806172</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3930,6 +4090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637493</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4027,6 +4192,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639807</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4128,6 +4298,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637504</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4229,6 +4404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637505</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4330,6 +4510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4427,6 +4612,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640304</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4524,6 +4714,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640305</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4625,6 +4820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638604</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4745,6 +4945,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805657</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4846,6 +5051,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637492</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4947,6 +5157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638655</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5048,6 +5263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638657</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5145,6 +5365,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639829</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5242,6 +5467,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640302</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5343,6 +5573,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638616</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5444,6 +5679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638617</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5545,6 +5785,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638618</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5642,6 +5887,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639810</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5739,6 +5989,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640283</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5840,6 +6095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637497</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5941,6 +6201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638635</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6042,6 +6307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638637</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6143,6 +6413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638638</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6244,6 +6519,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638640</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6345,6 +6625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638641</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6442,6 +6727,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639818</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6539,6 +6829,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639819</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6659,6 +6954,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805719</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6758,6 +7058,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638610</t>
         </is>
       </c>
     </row>
@@ -6865,6 +7170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638598</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6962,6 +7272,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639802</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7059,6 +7374,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639803</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7156,6 +7476,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640279</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7258,6 +7583,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478777</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7364,6 +7694,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66478778</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7465,6 +7800,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791814</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7585,6 +7925,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805573</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7682,6 +8027,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118633005</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7783,6 +8133,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638632</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7880,6 +8235,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639815</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7977,6 +8337,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639816</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8074,6 +8439,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639817</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8171,6 +8541,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640296</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8309,6 +8684,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118844165</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8433,6 +8813,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805702</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8534,6 +8919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638619</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8631,6 +9021,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641126</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8737,6 +9132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638605</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8843,6 +9243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638606</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8949,6 +9354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638607</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9055,6 +9465,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638608</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9157,6 +9572,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639806</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9259,6 +9679,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640300</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9361,6 +9786,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640301</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9463,6 +9893,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629700</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9567,6 +10002,11 @@
       <c r="AY88" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118636096</t>
         </is>
       </c>
     </row>
@@ -9671,6 +10111,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791849</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9768,6 +10213,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118626762</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9865,6 +10315,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118628010</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9962,6 +10417,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629196</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10059,6 +10519,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629307</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10156,6 +10621,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629765</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10257,6 +10727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637498</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10358,6 +10833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637499</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10464,6 +10944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638642</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10570,6 +11055,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638643</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10676,6 +11166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638644</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10782,6 +11277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638645</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10888,6 +11388,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638646</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10994,6 +11499,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638647</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11100,6 +11610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638648</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11206,6 +11721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638649</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11312,6 +11832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638650</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11418,6 +11943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638651</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11524,6 +12054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638652</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11630,6 +12165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638653</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11732,6 +12272,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639820</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11834,6 +12379,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639821</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11931,6 +12481,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639822</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12028,6 +12583,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639823</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12125,6 +12685,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639824</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12222,6 +12787,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639825</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12319,6 +12889,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639826</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12416,6 +12991,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639827</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12513,6 +13093,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640297</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12610,6 +13195,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640298</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12707,6 +13297,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640299</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12804,6 +13399,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641115</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12901,6 +13501,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641117</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12998,6 +13603,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641119</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13095,6 +13705,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641121</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13196,6 +13811,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118685271</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13297,6 +13917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118924479</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13394,6 +14019,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119125380</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13491,6 +14121,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134913225</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13588,6 +14223,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134913452</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13694,6 +14334,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134933656</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13795,6 +14440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638654</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13892,6 +14542,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641123</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13993,6 +14648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638614</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14090,6 +14750,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640281</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14187,6 +14852,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640282</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14307,6 +14977,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103805638</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14408,6 +15083,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637495</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14509,6 +15189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638621</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14610,6 +15295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638622</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14711,6 +15401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638623</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14812,6 +15507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638625</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14913,6 +15613,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638626</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15014,6 +15719,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638628</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15115,6 +15825,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638629</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15216,6 +15931,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638630</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15317,6 +16037,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638631</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15414,6 +16139,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639811</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15511,6 +16241,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639812</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15608,6 +16343,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639813</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15705,6 +16445,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639814</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15802,6 +16547,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640284</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15899,6 +16649,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640285</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15996,6 +16751,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640286</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16093,6 +16853,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640287</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16190,6 +16955,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640288</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16287,6 +17057,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640290</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16384,6 +17159,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640291</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16481,6 +17261,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640292</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16578,6 +17363,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640293</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16675,6 +17465,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640294</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16772,6 +17567,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640295</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16869,6 +17669,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118641113</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16974,6 +17779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638599</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17079,6 +17889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638600</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17184,6 +17999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638601</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17289,6 +18109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118638602</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17386,6 +18211,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639804</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17483,6 +18313,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639805</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17581,8 +18416,182 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640280</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1231-2025 artfynd.xlsx
+++ b/artfynd/S 1231-2025 artfynd.xlsx
@@ -14030,7 +14030,7 @@
         <v>134913225</v>
       </c>
       <c r="B127" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>134913452</v>
       </c>
       <c r="B128" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>134933656</v>
       </c>
       <c r="B129" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
